--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.89121546070868</v>
+        <v>7.61982251236516</v>
       </c>
       <c r="D2" t="n">
-        <v>35.64200611494453</v>
+        <v>5.791825993678486</v>
       </c>
       <c r="E2" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F2" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.18602229963592</v>
+        <v>7.992728623690838</v>
       </c>
       <c r="D3" t="n">
-        <v>24.1560380078033</v>
+        <v>3.925356176268036</v>
       </c>
       <c r="E3" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F3" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.86808797858796</v>
+        <v>6.966064296520543</v>
       </c>
       <c r="D4" t="n">
-        <v>13.93453949400298</v>
+        <v>2.264362667775484</v>
       </c>
       <c r="E4" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F4" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.02631322921357</v>
+        <v>5.691775899747205</v>
       </c>
       <c r="D5" t="n">
-        <v>37.72202528648155</v>
+        <v>6.129829109053252</v>
       </c>
       <c r="E5" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F5" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.18299126308063</v>
+        <v>5.554736080250603</v>
       </c>
       <c r="D6" t="n">
-        <v>16.53696974542223</v>
+        <v>2.687257583631113</v>
       </c>
       <c r="E6" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F6" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.68265308106883</v>
+        <v>3.198431125673685</v>
       </c>
       <c r="D7" t="n">
-        <v>38.7227123197195</v>
+        <v>6.292440751954419</v>
       </c>
       <c r="E7" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F7" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.50767086721785</v>
+        <v>4.957496515922901</v>
       </c>
       <c r="D8" t="n">
-        <v>34.68970813066485</v>
+        <v>5.637077571233039</v>
       </c>
       <c r="E8" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F8" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.32781924867903</v>
+        <v>3.790770627910343</v>
       </c>
       <c r="D9" t="n">
-        <v>2.813744277039826</v>
+        <v>0.4572334450189717</v>
       </c>
       <c r="E9" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F9" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.64584255846228</v>
+        <v>3.02994941575012</v>
       </c>
       <c r="D10" t="n">
-        <v>31.18834658756554</v>
+        <v>5.068106320479401</v>
       </c>
       <c r="E10" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F10" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.49516963681878</v>
+        <v>2.680465065983052</v>
       </c>
       <c r="D11" t="n">
-        <v>22.71808061287277</v>
+        <v>3.691688099591825</v>
       </c>
       <c r="E11" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F11" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.421341667583919</v>
+        <v>1.368468020982387</v>
       </c>
       <c r="D12" t="n">
-        <v>47.47768008251464</v>
+        <v>7.715123013408629</v>
       </c>
       <c r="E12" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F12" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.65596651610908</v>
+        <v>5.956594558867726</v>
       </c>
       <c r="D13" t="n">
-        <v>31.02082801365382</v>
+        <v>5.040884552218746</v>
       </c>
       <c r="E13" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F13" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.72001363776437</v>
+        <v>3.042002216136711</v>
       </c>
       <c r="D14" t="n">
-        <v>49.24542225684561</v>
+        <v>8.002381116737412</v>
       </c>
       <c r="E14" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F14" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.79349608593897</v>
+        <v>2.728943113965082</v>
       </c>
       <c r="D15" t="n">
-        <v>60.9749202668737</v>
+        <v>9.908424543366976</v>
       </c>
       <c r="E15" t="n">
-        <v>12.24572367206951</v>
+        <v>1.989930096711295</v>
       </c>
       <c r="F15" t="n">
-        <v>14.73928605991472</v>
+        <v>2.395133984736142</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
